--- a/artfynd/S 2739-2022 artfynd.xlsx
+++ b/artfynd/S 2739-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY62"/>
+  <dimension ref="A1:AZ62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -777,6 +782,11 @@
           <t>Gemensamma artsatsningar</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82697042</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
           <t>Utsjöbanksinventeringen, U2</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82715570</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -992,6 +1007,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108741246</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1112,6 +1132,11 @@
           <t>Gemensamma artsatsningar</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82696985</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1232,6 +1257,11 @@
           <t>Gemensamma artsatsningar</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82697901</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1352,6 +1382,11 @@
           <t>Gemensamma artsatsningar</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82697882</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1463,6 +1498,11 @@
           <t>Tommy Knutsson - Import Fynddatabas 2013</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/253656</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1577,6 +1617,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99115463</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1705,6 +1750,11 @@
           <t>Gemensamma artsatsningar</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82696983</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1838,6 +1888,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82738567</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1953,6 +2008,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108724201</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2067,6 +2127,11 @@
       <c r="AY13" t="inlineStr">
         <is>
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/681679</t>
         </is>
       </c>
     </row>
@@ -2174,6 +2239,11 @@
           <t>Gemensamma artsatsningar</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82697052</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2284,6 +2354,11 @@
           <t>Gemensamma artsatsningar</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82696970</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2410,6 +2485,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106126327</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2534,6 +2614,11 @@
       <c r="AY17" t="inlineStr">
         <is>
           <t>Skyddsvärda träd</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106126328</t>
         </is>
       </c>
     </row>
@@ -2641,6 +2726,11 @@
           <t>Gemensamma artsatsningar</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82698982</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2761,6 +2851,11 @@
           <t>Gemensamma artsatsningar</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82697889</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2866,6 +2961,11 @@
           <t>Gemensamma artsatsningar</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82698985</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2982,6 +3082,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2272661</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3118,6 +3223,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110279429</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3254,6 +3364,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133127071</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3375,6 +3490,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65810112</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3491,6 +3611,11 @@
           <t>Gemensamma artsatsningar</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82697054</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3641,6 +3766,11 @@
           <t>ÅGP Skärrande gräshoppa N Öland (Calluna_OKL0003)</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60698345</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3787,6 +3917,11 @@
           <t>ÅGP Skärrande gräshoppa N Öland (Calluna_OKL0003)</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60698347</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3891,6 +4026,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64721396</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3998,6 +4138,11 @@
           <t>Gemensamma artsatsningar</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82697033</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4109,6 +4254,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2210317</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4220,6 +4370,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2210318</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4324,6 +4479,11 @@
       <c r="AY32" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2223673</t>
         </is>
       </c>
     </row>
@@ -4433,6 +4593,11 @@
       <c r="AY33" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64721316</t>
         </is>
       </c>
     </row>
@@ -4537,6 +4702,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109482624</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4645,6 +4815,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64721431</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4755,6 +4930,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99432761</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4861,6 +5041,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3511772</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4962,6 +5147,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6792918</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5072,6 +5262,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106118327</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5182,6 +5377,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106118329</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5292,6 +5492,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106118334</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5402,6 +5607,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106118335</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5512,6 +5722,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106118336</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5622,6 +5837,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106118337</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5737,6 +5957,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106118338</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5847,6 +6072,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106120069</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5957,6 +6187,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106120070</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6067,6 +6302,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106120071</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6182,6 +6422,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106120072</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6288,6 +6533,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3385010</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6389,6 +6639,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6792891</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6488,6 +6743,11 @@
       <c r="AY52" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6792879</t>
         </is>
       </c>
     </row>
@@ -6594,6 +6854,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16178533</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6705,6 +6970,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4958603</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6814,6 +7084,11 @@
       <c r="AY55" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4958604</t>
         </is>
       </c>
     </row>
@@ -6920,6 +7195,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64721294</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7030,6 +7310,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106121020</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7140,6 +7425,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106121021</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7250,6 +7540,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106121022</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7360,6 +7655,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106121024</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7470,6 +7770,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106121025</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7581,8 +7886,76 @@
           <t>Tommy Knutsson - Import Fynddatabas 2013</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6526329</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>